--- a/files/Conditional Formatting Excel Tutorial File.xlsx
+++ b/files/Conditional Formatting Excel Tutorial File.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/579481080490e445/Documents/Excel Series Excels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\advance_excel\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE12AABD-2C2A-4D60-B298-E861FD33474F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C3A983-F7C1-4C02-BEDE-8E61E37280FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5EA44D8F-79D3-45F5-A0F6-C7F47358B7ED}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Demographics" sheetId="1" r:id="rId1"/>
     <sheet name="Sales" sheetId="4" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Demographics!$A$1:$K$10</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -333,7 +336,38 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -347,9 +381,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -387,7 +421,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -493,7 +527,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -635,7 +669,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1022,7 +1056,46 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K10" xr:uid="{1027015F-D30F-450C-928C-DE78480974B7}"/>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{7A8DA3C8-EBB5-4AED-B0E3-2558DF46056F}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{7A8DA3C8-EBB5-4AED-B0E3-2558DF46056F}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>H1:H1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -1196,6 +1269,15 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:M2">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>